--- a/SuppXLS/Scen_NSV_TRADSL_TAX.xlsx
+++ b/SuppXLS/Scen_NSV_TRADSL_TAX.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x15 xr xr6 xr10">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" mc:Ignorable="x15 xr xr6 xr10">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22730"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Training material\DemoS_012\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{23CCB81E-028A-407F-9AF5-490150DDC9FC}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1905" yWindow="1905" windowWidth="21600" windowHeight="11385"/>
+    <workbookView xWindow="1905" yWindow="1905" windowWidth="21600" windowHeight="11385" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="TRADSL_TAX" sheetId="2" r:id="rId1"/>
+    <sheet name="TRADSL_TAX" sheetId="2" r:id="rId3"/>
   </sheets>
+  <definedNames/>
   <calcPr calcId="125725"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -28,18 +28,17 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Maurizio Gargiulo</author>
   </authors>
   <commentList>
-    <comment ref="B2" authorId="0" shapeId="0">
+    <comment ref="B2" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -52,58 +51,67 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="14">
+  <si>
+    <t>REG1</t>
+  </si>
+  <si>
+    <t>Cset_CN</t>
+  </si>
+  <si>
+    <t>FLO_TAX</t>
+  </si>
   <si>
     <t>Year</t>
   </si>
   <si>
+    <t>Attribute</t>
+  </si>
+  <si>
+    <t>TimeSlice</t>
+  </si>
+  <si>
+    <t>LimType</t>
+  </si>
+  <si>
+    <t>~TFM_INS</t>
+  </si>
+  <si>
     <t>Pset_PN</t>
   </si>
   <si>
-    <t>Cset_CN</t>
-  </si>
-  <si>
-    <t>Attribute</t>
-  </si>
-  <si>
-    <t>LimType</t>
-  </si>
-  <si>
-    <t>~TFM_INS</t>
-  </si>
-  <si>
-    <t>TimeSlice</t>
+    <t>REG2</t>
+  </si>
+  <si>
+    <t>jlkj</t>
+  </si>
+  <si>
+    <t>TC*</t>
+  </si>
+  <si>
+    <t>TRADSL</t>
   </si>
   <si>
     <t>Trans - Insert</t>
-  </si>
-  <si>
-    <t>REG2</t>
-  </si>
-  <si>
-    <t>REG1</t>
-  </si>
-  <si>
-    <t>TRADSL</t>
-  </si>
-  <si>
-    <t>FLO_TAX</t>
-  </si>
-  <si>
-    <t>TC*</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -132,7 +140,6 @@
     <font>
       <b/>
       <sz val="8"/>
-      <color indexed="81"/>
       <name val="Tahoma"/>
       <family val="2"/>
     </font>
@@ -169,36 +176,135 @@
       <left/>
       <right/>
       <top style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </top>
       <bottom style="medium">
-        <color indexed="64"/>
+        <color auto="1"/>
       </bottom>
-      <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+  <cellStyleXfs count="22">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment/>
+      <protection/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="8">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 10" xfId="1"/>
-    <cellStyle name="Normale_Scen_UC_IND-StrucConst" xfId="2"/>
+    <cellStyle name="Percent" xfId="15" builtinId="5"/>
+    <cellStyle name="Currency" xfId="16" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="17" builtinId="7"/>
+    <cellStyle name="Comma" xfId="18" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="19" builtinId="6"/>
+    <cellStyle name="Normal 10" xfId="20"/>
+    <cellStyle name="Normale_Scen_UC_IND-StrucConst" xfId="21"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -211,7 +317,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
@@ -225,12 +331,12 @@
       <xdr:row>10</xdr:row>
       <xdr:rowOff>111125</xdr:rowOff>
     </xdr:to>
-    <xdr:sp macro="" textlink="">
+    <xdr:sp>
       <xdr:nvSpPr>
         <xdr:cNvPr id="4" name="TextBox 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{31603209-A7CB-4616-B60C-63BFB6A8A57B}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{31603209-a7cb-4616-b60c-63bfb6a8a57b}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -238,12 +344,10 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="608135" y="1531327"/>
-          <a:ext cx="4922471" cy="492125"/>
+          <a:off x="609600" y="1533525"/>
+          <a:ext cx="4905375" cy="495300"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
+        <a:prstGeom prst="rect"/>
         <a:solidFill>
           <a:schemeClr val="accent6">
             <a:lumMod val="20000"/>
@@ -252,7 +356,7 @@
         </a:solidFill>
         <a:ln w="9525" cmpd="sng">
           <a:solidFill>
-            <a:schemeClr val="lt1">
+            <a:schemeClr val="bg1">
               <a:shade val="50000"/>
             </a:schemeClr>
           </a:solidFill>
@@ -260,26 +364,27 @@
       </xdr:spPr>
       <xdr:style>
         <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
+          <a:srgbClr val="000000"/>
         </a:lnRef>
         <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
+          <a:srgbClr val="000000"/>
         </a:fillRef>
         <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
+          <a:srgbClr val="000000"/>
         </a:effectRef>
         <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
+          <a:schemeClr val="tx1"/>
         </a:fontRef>
       </xdr:style>
       <xdr:txBody>
         <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
         <a:lstStyle/>
         <a:p>
+          <a:pPr/>
           <a:r>
             <a:rPr lang="en-GB" sz="1100">
               <a:solidFill>
-                <a:schemeClr val="dk1"/>
+                <a:schemeClr val="tx1"/>
               </a:solidFill>
               <a:effectLst/>
               <a:latin typeface="+mn-lt"/>
@@ -291,7 +396,7 @@
           <a:r>
             <a:rPr lang="en-GB" sz="1100" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="dk1"/>
+                <a:schemeClr val="tx1"/>
               </a:solidFill>
               <a:effectLst/>
               <a:latin typeface="+mn-lt"/>
@@ -303,7 +408,7 @@
           <a:r>
             <a:rPr lang="en-GB" sz="1100">
               <a:solidFill>
-                <a:schemeClr val="dk1"/>
+                <a:schemeClr val="tx1"/>
               </a:solidFill>
               <a:effectLst/>
               <a:latin typeface="+mn-lt"/>
@@ -315,7 +420,7 @@
           <a:r>
             <a:rPr lang="en-GB" sz="1100" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="dk1"/>
+                <a:schemeClr val="tx1"/>
               </a:solidFill>
               <a:effectLst/>
               <a:latin typeface="+mn-lt"/>
@@ -327,7 +432,7 @@
           <a:r>
             <a:rPr lang="en-GB" sz="1100">
               <a:solidFill>
-                <a:schemeClr val="dk1"/>
+                <a:schemeClr val="tx1"/>
               </a:solidFill>
               <a:effectLst/>
               <a:latin typeface="+mn-lt"/>
@@ -337,6 +442,9 @@
             <a:t>.</a:t>
           </a:r>
           <a:endParaRPr lang="en-GB">
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
             <a:effectLst/>
           </a:endParaRPr>
         </a:p>
@@ -667,59 +775,59 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:P8"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.5703125" customWidth="1"/>
-    <col min="5" max="5" width="5.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="10.7109375" customWidth="1"/>
-    <col min="8" max="9" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.1428571428571" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.85714285714286" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.5714285714286" customWidth="1"/>
+    <col min="5" max="5" width="5.14285714285714" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="10.7142857142857" customWidth="1"/>
+    <col min="8" max="9" width="8.42857142857143" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" ht="15">
       <c r="A1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="2:9" ht="15">
+      <c r="B2" s="1" t="s">
         <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B2" s="1" t="s">
-        <v>5</v>
       </c>
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
     </row>
-    <row r="3" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:9" ht="15.75" thickBot="1">
       <c r="B3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="D3" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="E3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="F3" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="G3" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="H3" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="H3" s="5" t="s">
+      <c r="I3" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="I3" s="5" t="s">
+    </row>
+    <row r="4" spans="4:9" ht="15">
+      <c r="D4" t="s">
         <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="D4" t="s">
-        <v>11</v>
       </c>
       <c r="E4">
         <v>2015</v>
@@ -731,15 +839,15 @@
         <v>10</v>
       </c>
       <c r="H4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I4" t="s">
         <v>12</v>
       </c>
-      <c r="I4" t="s">
-        <v>10</v>
-      </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="4:9" ht="15">
       <c r="D5" t="s">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="E5">
         <v>2050</v>
@@ -751,15 +859,15 @@
         <v>20</v>
       </c>
       <c r="H5" t="s">
+        <v>11</v>
+      </c>
+      <c r="I5" t="s">
         <v>12</v>
       </c>
-      <c r="I5" t="s">
-        <v>10</v>
-      </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="4:9" ht="15">
       <c r="D6" t="s">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -771,15 +879,20 @@
         <v>5</v>
       </c>
       <c r="H6" t="s">
+        <v>11</v>
+      </c>
+      <c r="I6" t="s">
         <v>12</v>
       </c>
-      <c r="I6" t="s">
+    </row>
+    <row r="8" spans="16:16" ht="15">
+      <c r="P8" t="s">
         <v>10</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-  <legacyDrawing r:id="rId2"/>
+  <drawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
 </worksheet>
 </file>
--- a/SuppXLS/Scen_NSV_TRADSL_TAX.xlsx
+++ b/SuppXLS/Scen_NSV_TRADSL_TAX.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" mc:Ignorable="x15 xr xr6 xr10">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x15 xr xr6 xr10">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22730"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Training material\DemoS_012\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{23CCB81E-028A-407F-9AF5-490150DDC9FC}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1905" yWindow="1905" windowWidth="21600" windowHeight="11385" activeTab="0"/>
+    <workbookView xWindow="1905" yWindow="1905" windowWidth="21600" windowHeight="11385"/>
   </bookViews>
   <sheets>
-    <sheet name="TRADSL_TAX" sheetId="2" r:id="rId3"/>
+    <sheet name="TRADSL_TAX" sheetId="2" r:id="rId1"/>
   </sheets>
-  <definedNames/>
   <calcPr calcId="125725"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -28,17 +28,18 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Maurizio Gargiulo</author>
   </authors>
   <commentList>
-    <comment ref="B2" authorId="0">
+    <comment ref="B2" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="8"/>
+            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -51,67 +52,58 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="13">
+  <si>
+    <t>Year</t>
+  </si>
+  <si>
+    <t>Pset_PN</t>
+  </si>
+  <si>
+    <t>Cset_CN</t>
+  </si>
+  <si>
+    <t>Attribute</t>
+  </si>
+  <si>
+    <t>LimType</t>
+  </si>
+  <si>
+    <t>~TFM_INS</t>
+  </si>
+  <si>
+    <t>TimeSlice</t>
+  </si>
+  <si>
+    <t>Trans - Insert</t>
+  </si>
+  <si>
+    <t>REG2</t>
+  </si>
   <si>
     <t>REG1</t>
   </si>
   <si>
-    <t>Cset_CN</t>
+    <t>TRADSL</t>
   </si>
   <si>
     <t>FLO_TAX</t>
   </si>
   <si>
-    <t>Year</t>
-  </si>
-  <si>
-    <t>Attribute</t>
-  </si>
-  <si>
-    <t>TimeSlice</t>
-  </si>
-  <si>
-    <t>LimType</t>
-  </si>
-  <si>
-    <t>~TFM_INS</t>
-  </si>
-  <si>
-    <t>Pset_PN</t>
-  </si>
-  <si>
-    <t>REG2</t>
-  </si>
-  <si>
-    <t>jlkj</t>
-  </si>
-  <si>
     <t>TC*</t>
-  </si>
-  <si>
-    <t>TRADSL</t>
-  </si>
-  <si>
-    <t>Trans - Insert</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="7">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -140,6 +132,7 @@
     <font>
       <b/>
       <sz val="8"/>
+      <color indexed="81"/>
       <name val="Tahoma"/>
       <family val="2"/>
     </font>
@@ -176,135 +169,36 @@
       <left/>
       <right/>
       <top style="thin">
-        <color auto="1"/>
+        <color indexed="64"/>
       </top>
       <bottom style="medium">
-        <color auto="1"/>
+        <color indexed="64"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="22">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment/>
-      <protection/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
-      <alignment/>
-      <protection/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment/>
-      <protection/>
-    </xf>
+  <cellStyleXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="8">
+  <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Percent" xfId="15" builtinId="5"/>
-    <cellStyle name="Currency" xfId="16" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="17" builtinId="7"/>
-    <cellStyle name="Comma" xfId="18" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="19" builtinId="6"/>
-    <cellStyle name="Normal 10" xfId="20"/>
-    <cellStyle name="Normale_Scen_UC_IND-StrucConst" xfId="21"/>
+    <cellStyle name="Normal 10" xfId="1"/>
+    <cellStyle name="Normale_Scen_UC_IND-StrucConst" xfId="2"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -317,7 +211,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
@@ -331,12 +225,12 @@
       <xdr:row>10</xdr:row>
       <xdr:rowOff>111125</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
         <xdr:cNvPr id="4" name="TextBox 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{31603209-a7cb-4616-b60c-63bfb6a8a57b}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{31603209-A7CB-4616-B60C-63BFB6A8A57B}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -344,10 +238,12 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="609600" y="1533525"/>
-          <a:ext cx="4905375" cy="495300"/>
+          <a:off x="608135" y="1531327"/>
+          <a:ext cx="4922471" cy="492125"/>
         </a:xfrm>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
         <a:solidFill>
           <a:schemeClr val="accent6">
             <a:lumMod val="20000"/>
@@ -356,7 +252,7 @@
         </a:solidFill>
         <a:ln w="9525" cmpd="sng">
           <a:solidFill>
-            <a:schemeClr val="bg1">
+            <a:schemeClr val="lt1">
               <a:shade val="50000"/>
             </a:schemeClr>
           </a:solidFill>
@@ -364,27 +260,26 @@
       </xdr:spPr>
       <xdr:style>
         <a:lnRef idx="0">
-          <a:srgbClr val="000000"/>
+          <a:scrgbClr r="0" g="0" b="0"/>
         </a:lnRef>
         <a:fillRef idx="0">
-          <a:srgbClr val="000000"/>
+          <a:scrgbClr r="0" g="0" b="0"/>
         </a:fillRef>
         <a:effectRef idx="0">
-          <a:srgbClr val="000000"/>
+          <a:scrgbClr r="0" g="0" b="0"/>
         </a:effectRef>
         <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
+          <a:schemeClr val="dk1"/>
         </a:fontRef>
       </xdr:style>
       <xdr:txBody>
         <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
         <a:lstStyle/>
         <a:p>
-          <a:pPr/>
           <a:r>
             <a:rPr lang="en-GB" sz="1100">
               <a:solidFill>
-                <a:schemeClr val="tx1"/>
+                <a:schemeClr val="dk1"/>
               </a:solidFill>
               <a:effectLst/>
               <a:latin typeface="+mn-lt"/>
@@ -396,7 +291,7 @@
           <a:r>
             <a:rPr lang="en-GB" sz="1100" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="tx1"/>
+                <a:schemeClr val="dk1"/>
               </a:solidFill>
               <a:effectLst/>
               <a:latin typeface="+mn-lt"/>
@@ -408,7 +303,7 @@
           <a:r>
             <a:rPr lang="en-GB" sz="1100">
               <a:solidFill>
-                <a:schemeClr val="tx1"/>
+                <a:schemeClr val="dk1"/>
               </a:solidFill>
               <a:effectLst/>
               <a:latin typeface="+mn-lt"/>
@@ -420,7 +315,7 @@
           <a:r>
             <a:rPr lang="en-GB" sz="1100" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="tx1"/>
+                <a:schemeClr val="dk1"/>
               </a:solidFill>
               <a:effectLst/>
               <a:latin typeface="+mn-lt"/>
@@ -432,7 +327,7 @@
           <a:r>
             <a:rPr lang="en-GB" sz="1100">
               <a:solidFill>
-                <a:schemeClr val="tx1"/>
+                <a:schemeClr val="dk1"/>
               </a:solidFill>
               <a:effectLst/>
               <a:latin typeface="+mn-lt"/>
@@ -442,9 +337,6 @@
             <a:t>.</a:t>
           </a:r>
           <a:endParaRPr lang="en-GB">
-            <a:solidFill>
-              <a:srgbClr val="000000"/>
-            </a:solidFill>
             <a:effectLst/>
           </a:endParaRPr>
         </a:p>
@@ -775,59 +667,59 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:I6"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="10.1428571428571" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.85714285714286" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.5714285714286" customWidth="1"/>
-    <col min="5" max="5" width="5.14285714285714" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="10.7142857142857" customWidth="1"/>
-    <col min="8" max="9" width="8.42857142857143" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.5703125" customWidth="1"/>
+    <col min="5" max="5" width="5.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="10.7109375" customWidth="1"/>
+    <col min="8" max="9" width="8.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="15">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
-    <row r="2" spans="2:9" ht="15">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
     </row>
-    <row r="3" spans="2:9" ht="15.75" thickBot="1">
+    <row r="3" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
-    <row r="4" spans="4:9" ht="15">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="D4" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="E4">
         <v>2015</v>
@@ -839,15 +731,15 @@
         <v>10</v>
       </c>
       <c r="H4" t="s">
+        <v>12</v>
+      </c>
+      <c r="I4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="D5" t="s">
         <v>11</v>
-      </c>
-      <c r="I4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="4:9" ht="15">
-      <c r="D5" t="s">
-        <v>2</v>
       </c>
       <c r="E5">
         <v>2050</v>
@@ -859,15 +751,15 @@
         <v>20</v>
       </c>
       <c r="H5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="D6" t="s">
         <v>11</v>
-      </c>
-      <c r="I5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" spans="4:9" ht="15">
-      <c r="D6" t="s">
-        <v>2</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -879,20 +771,15 @@
         <v>5</v>
       </c>
       <c r="H6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="16:16" ht="15">
-      <c r="P8" t="s">
         <v>10</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId2"/>
-  <legacyDrawing r:id="rId3"/>
+  <drawing r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/SuppXLS/Scen_NSV_TRADSL_TAX.xlsx
+++ b/SuppXLS/Scen_NSV_TRADSL_TAX.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x15 xr xr6 xr10">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" mc:Ignorable="x15 xr xr6 xr10">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22730"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Training material\DemoS_012\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{23CCB81E-028A-407F-9AF5-490150DDC9FC}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1905" yWindow="1905" windowWidth="21600" windowHeight="11385"/>
+    <workbookView xWindow="1905" yWindow="1905" windowWidth="21600" windowHeight="11385" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="TRADSL_TAX" sheetId="2" r:id="rId1"/>
+    <sheet name="TRADSL_TAX" sheetId="2" r:id="rId3"/>
   </sheets>
+  <definedNames/>
   <calcPr calcId="125725"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -28,18 +28,17 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Maurizio Gargiulo</author>
   </authors>
   <commentList>
-    <comment ref="B2" authorId="0" shapeId="0">
+    <comment ref="B2" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -52,58 +51,67 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="14">
+  <si>
+    <t>REG2</t>
+  </si>
+  <si>
+    <t>Attribute</t>
+  </si>
+  <si>
+    <t>LimType</t>
+  </si>
+  <si>
+    <t>Pset_PN</t>
+  </si>
+  <si>
+    <t>Cset_CN</t>
+  </si>
+  <si>
+    <t>TC*</t>
+  </si>
+  <si>
+    <t>FLO_TAX</t>
+  </si>
+  <si>
+    <t>TRADSL</t>
+  </si>
   <si>
     <t>Year</t>
   </si>
   <si>
-    <t>Pset_PN</t>
-  </si>
-  <si>
-    <t>Cset_CN</t>
-  </si>
-  <si>
-    <t>Attribute</t>
-  </si>
-  <si>
-    <t>LimType</t>
+    <t>REG1</t>
+  </si>
+  <si>
+    <t>Trans - Insert</t>
+  </si>
+  <si>
+    <t>TimeSlice</t>
   </si>
   <si>
     <t>~TFM_INS</t>
   </si>
   <si>
-    <t>TimeSlice</t>
-  </si>
-  <si>
-    <t>Trans - Insert</t>
-  </si>
-  <si>
-    <t>REG2</t>
-  </si>
-  <si>
-    <t>REG1</t>
-  </si>
-  <si>
-    <t>TRADSL</t>
-  </si>
-  <si>
-    <t>FLO_TAX</t>
-  </si>
-  <si>
-    <t>TC*</t>
+    <t>uolkj</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -132,7 +140,6 @@
     <font>
       <b/>
       <sz val="8"/>
-      <color indexed="81"/>
       <name val="Tahoma"/>
       <family val="2"/>
     </font>
@@ -169,36 +176,135 @@
       <left/>
       <right/>
       <top style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </top>
       <bottom style="medium">
-        <color indexed="64"/>
+        <color auto="1"/>
       </bottom>
-      <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+  <cellStyleXfs count="22">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment/>
+      <protection/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="8">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 10" xfId="1"/>
-    <cellStyle name="Normale_Scen_UC_IND-StrucConst" xfId="2"/>
+    <cellStyle name="Percent" xfId="15" builtinId="5"/>
+    <cellStyle name="Currency" xfId="16" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="17" builtinId="7"/>
+    <cellStyle name="Comma" xfId="18" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="19" builtinId="6"/>
+    <cellStyle name="Normal 10" xfId="20"/>
+    <cellStyle name="Normale_Scen_UC_IND-StrucConst" xfId="21"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -211,7 +317,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
@@ -225,12 +331,12 @@
       <xdr:row>10</xdr:row>
       <xdr:rowOff>111125</xdr:rowOff>
     </xdr:to>
-    <xdr:sp macro="" textlink="">
+    <xdr:sp>
       <xdr:nvSpPr>
         <xdr:cNvPr id="4" name="TextBox 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{31603209-A7CB-4616-B60C-63BFB6A8A57B}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{31603209-a7cb-4616-b60c-63bfb6a8a57b}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -238,12 +344,10 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="608135" y="1531327"/>
-          <a:ext cx="4922471" cy="492125"/>
+          <a:off x="609600" y="1533525"/>
+          <a:ext cx="4905375" cy="495300"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
+        <a:prstGeom prst="rect"/>
         <a:solidFill>
           <a:schemeClr val="accent6">
             <a:lumMod val="20000"/>
@@ -252,7 +356,7 @@
         </a:solidFill>
         <a:ln w="9525" cmpd="sng">
           <a:solidFill>
-            <a:schemeClr val="lt1">
+            <a:schemeClr val="bg1">
               <a:shade val="50000"/>
             </a:schemeClr>
           </a:solidFill>
@@ -260,26 +364,27 @@
       </xdr:spPr>
       <xdr:style>
         <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
+          <a:srgbClr val="000000"/>
         </a:lnRef>
         <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
+          <a:srgbClr val="000000"/>
         </a:fillRef>
         <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
+          <a:srgbClr val="000000"/>
         </a:effectRef>
         <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
+          <a:schemeClr val="tx1"/>
         </a:fontRef>
       </xdr:style>
       <xdr:txBody>
         <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
         <a:lstStyle/>
         <a:p>
+          <a:pPr/>
           <a:r>
             <a:rPr lang="en-GB" sz="1100">
               <a:solidFill>
-                <a:schemeClr val="dk1"/>
+                <a:schemeClr val="tx1"/>
               </a:solidFill>
               <a:effectLst/>
               <a:latin typeface="+mn-lt"/>
@@ -291,7 +396,7 @@
           <a:r>
             <a:rPr lang="en-GB" sz="1100" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="dk1"/>
+                <a:schemeClr val="tx1"/>
               </a:solidFill>
               <a:effectLst/>
               <a:latin typeface="+mn-lt"/>
@@ -303,7 +408,7 @@
           <a:r>
             <a:rPr lang="en-GB" sz="1100">
               <a:solidFill>
-                <a:schemeClr val="dk1"/>
+                <a:schemeClr val="tx1"/>
               </a:solidFill>
               <a:effectLst/>
               <a:latin typeface="+mn-lt"/>
@@ -315,7 +420,7 @@
           <a:r>
             <a:rPr lang="en-GB" sz="1100" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="dk1"/>
+                <a:schemeClr val="tx1"/>
               </a:solidFill>
               <a:effectLst/>
               <a:latin typeface="+mn-lt"/>
@@ -327,7 +432,7 @@
           <a:r>
             <a:rPr lang="en-GB" sz="1100">
               <a:solidFill>
-                <a:schemeClr val="dk1"/>
+                <a:schemeClr val="tx1"/>
               </a:solidFill>
               <a:effectLst/>
               <a:latin typeface="+mn-lt"/>
@@ -337,6 +442,9 @@
             <a:t>.</a:t>
           </a:r>
           <a:endParaRPr lang="en-GB">
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
             <a:effectLst/>
           </a:endParaRPr>
         </a:p>
@@ -667,59 +775,59 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:K6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.5703125" customWidth="1"/>
-    <col min="5" max="5" width="5.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="10.7109375" customWidth="1"/>
-    <col min="8" max="9" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.1428571428571" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.85714285714286" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.5714285714286" customWidth="1"/>
+    <col min="5" max="5" width="5.14285714285714" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="10.7142857142857" customWidth="1"/>
+    <col min="8" max="9" width="8.42857142857143" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" ht="15">
       <c r="A1" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:9" ht="15">
       <c r="B2" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
     </row>
-    <row r="3" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:9" ht="15.75" thickBot="1">
       <c r="B3" s="3" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F3" s="4" t="s">
         <v>9</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="4:9" ht="15">
       <c r="D4" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E4">
         <v>2015</v>
@@ -731,15 +839,15 @@
         <v>10</v>
       </c>
       <c r="H4" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="I4" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="4:11" ht="15">
       <c r="D5" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E5">
         <v>2050</v>
@@ -751,15 +859,18 @@
         <v>20</v>
       </c>
       <c r="H5" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="I5" t="s">
-        <v>10</v>
+        <v>7</v>
+      </c>
+      <c r="K5" t="s">
+        <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="4:9" ht="15">
       <c r="D6" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -771,15 +882,15 @@
         <v>5</v>
       </c>
       <c r="H6" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="I6" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-  <legacyDrawing r:id="rId2"/>
+  <drawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
 </worksheet>
 </file>
--- a/SuppXLS/Scen_NSV_TRADSL_TAX.xlsx
+++ b/SuppXLS/Scen_NSV_TRADSL_TAX.xlsx
@@ -53,53 +53,54 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="14">
   <si>
+    <t>REG1</t>
+  </si>
+  <si>
+    <t>Cset_CN</t>
+  </si>
+  <si>
+    <t>FLO_TAX</t>
+  </si>
+  <si>
+    <t>Year</t>
+  </si>
+  <si>
+    <t>Attribute</t>
+  </si>
+  <si>
+    <t>~TFM_INS</t>
+  </si>
+  <si>
+    <t>TimeSlice</t>
+  </si>
+  <si>
+    <t>Trans - Insert</t>
+  </si>
+  <si>
+    <t>Pset_PN</t>
+  </si>
+  <si>
     <t>REG2</t>
   </si>
   <si>
-    <t>Attribute</t>
+    <t xml:space="preserve">
+</t>
+  </si>
+  <si>
+    <t>TC*</t>
+  </si>
+  <si>
+    <t>TRADSL</t>
   </si>
   <si>
     <t>LimType</t>
-  </si>
-  <si>
-    <t>Pset_PN</t>
-  </si>
-  <si>
-    <t>Cset_CN</t>
-  </si>
-  <si>
-    <t>TC*</t>
-  </si>
-  <si>
-    <t>FLO_TAX</t>
-  </si>
-  <si>
-    <t>TRADSL</t>
-  </si>
-  <si>
-    <t>Year</t>
-  </si>
-  <si>
-    <t>REG1</t>
-  </si>
-  <si>
-    <t>Trans - Insert</t>
-  </si>
-  <si>
-    <t>TimeSlice</t>
-  </si>
-  <si>
-    <t>~TFM_INS</t>
-  </si>
-  <si>
-    <t>uolkj</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -141,6 +142,12 @@
       <b/>
       <sz val="8"/>
       <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -216,7 +223,7 @@
       <protection/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -225,6 +232,18 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" wrapText="1"/>
+      <protection/>
+    </xf>
   </cellXfs>
   <cellStyles count="8">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -789,45 +808,45 @@
   <sheetData>
     <row r="1" spans="1:1" ht="15">
       <c r="A1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="2" spans="2:9" ht="15">
       <c r="B2" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
     </row>
     <row r="3" spans="2:9" ht="15.75" thickBot="1">
       <c r="B3" s="3" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="D3" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="I3" s="5" t="s">
         <v>1</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="H3" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="I3" s="5" t="s">
-        <v>4</v>
       </c>
     </row>
     <row r="4" spans="4:9" ht="15">
       <c r="D4" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E4">
         <v>2015</v>
@@ -839,38 +858,38 @@
         <v>10</v>
       </c>
       <c r="H4" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="I4" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="4:11" ht="15">
-      <c r="D5" t="s">
-        <v>6</v>
-      </c>
-      <c r="E5">
+      <c r="D5" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E5" s="7">
         <v>2050</v>
       </c>
-      <c r="F5">
+      <c r="F5" s="7">
         <v>30</v>
       </c>
-      <c r="G5">
+      <c r="G5" s="7">
         <v>20</v>
       </c>
-      <c r="H5" t="s">
-        <v>5</v>
-      </c>
-      <c r="I5" t="s">
-        <v>7</v>
-      </c>
-      <c r="K5" t="s">
-        <v>13</v>
+      <c r="H5" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="I5" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="K5" s="8" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="4:9" ht="15">
       <c r="D6" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -882,10 +901,10 @@
         <v>5</v>
       </c>
       <c r="H6" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="I6" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/SuppXLS/Scen_NSV_TRADSL_TAX.xlsx
+++ b/SuppXLS/Scen_NSV_TRADSL_TAX.xlsx
@@ -51,49 +51,52 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="15">
+  <si>
+    <t>REG2</t>
+  </si>
+  <si>
+    <t>Attribute</t>
+  </si>
+  <si>
+    <t>TimeSlice</t>
+  </si>
+  <si>
+    <t>Pset_PN</t>
+  </si>
+  <si>
+    <t>Cset_CN</t>
+  </si>
+  <si>
+    <t>TRADSL</t>
+  </si>
+  <si>
+    <t>TC*</t>
+  </si>
+  <si>
+    <t>test</t>
+  </si>
+  <si>
+    <t>Year</t>
+  </si>
   <si>
     <t>REG1</t>
   </si>
   <si>
-    <t>Cset_CN</t>
+    <t>LimType</t>
+  </si>
+  <si>
+    <t>~TFM_INS</t>
+  </si>
+  <si>
+    <t>Trans - Insert</t>
   </si>
   <si>
     <t>FLO_TAX</t>
-  </si>
-  <si>
-    <t>Year</t>
-  </si>
-  <si>
-    <t>Attribute</t>
-  </si>
-  <si>
-    <t>~TFM_INS</t>
-  </si>
-  <si>
-    <t>TimeSlice</t>
-  </si>
-  <si>
-    <t>Trans - Insert</t>
-  </si>
-  <si>
-    <t>Pset_PN</t>
-  </si>
-  <si>
-    <t>REG2</t>
   </si>
   <si>
     <t xml:space="preserve">
 </t>
-  </si>
-  <si>
-    <t>TC*</t>
-  </si>
-  <si>
-    <t>TRADSL</t>
-  </si>
-  <si>
-    <t>LimType</t>
   </si>
 </sst>
 </file>
@@ -808,45 +811,45 @@
   <sheetData>
     <row r="1" spans="1:1" ht="15">
       <c r="A1" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2" spans="2:9" ht="15">
       <c r="B2" s="1" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
     </row>
     <row r="3" spans="2:9" ht="15.75" thickBot="1">
       <c r="B3" s="3" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="4:11" ht="15">
+      <c r="D4" t="s">
         <v>13</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="H3" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="I3" s="5" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="4:9" ht="15">
-      <c r="D4" t="s">
-        <v>2</v>
       </c>
       <c r="E4">
         <v>2015</v>
@@ -858,15 +861,18 @@
         <v>10</v>
       </c>
       <c r="H4" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="I4" t="s">
-        <v>12</v>
+        <v>5</v>
+      </c>
+      <c r="K4" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="4:11" ht="15">
       <c r="D5" s="6" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="E5" s="7">
         <v>2050</v>
@@ -878,18 +884,18 @@
         <v>20</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="K5" s="8" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="4:9" ht="15">
       <c r="D6" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -901,10 +907,10 @@
         <v>5</v>
       </c>
       <c r="H6" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="I6" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/SuppXLS/Scen_NSV_TRADSL_TAX.xlsx
+++ b/SuppXLS/Scen_NSV_TRADSL_TAX.xlsx
@@ -51,52 +51,49 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="14">
   <si>
     <t>REG2</t>
   </si>
   <si>
+    <t>FLO_TAX</t>
+  </si>
+  <si>
+    <t>TRADSL</t>
+  </si>
+  <si>
+    <t>REG1</t>
+  </si>
+  <si>
+    <t>Year</t>
+  </si>
+  <si>
+    <t>Trans - Insert</t>
+  </si>
+  <si>
+    <t>~TFM_INS</t>
+  </si>
+  <si>
     <t>Attribute</t>
   </si>
   <si>
-    <t>TimeSlice</t>
+    <t>Cset_CN</t>
   </si>
   <si>
     <t>Pset_PN</t>
   </si>
   <si>
-    <t>Cset_CN</t>
-  </si>
-  <si>
-    <t>TRADSL</t>
-  </si>
-  <si>
     <t>TC*</t>
-  </si>
-  <si>
-    <t>test</t>
-  </si>
-  <si>
-    <t>Year</t>
-  </si>
-  <si>
-    <t>REG1</t>
-  </si>
-  <si>
-    <t>LimType</t>
-  </si>
-  <si>
-    <t>~TFM_INS</t>
-  </si>
-  <si>
-    <t>Trans - Insert</t>
-  </si>
-  <si>
-    <t>FLO_TAX</t>
   </si>
   <si>
     <t xml:space="preserve">
 </t>
+  </si>
+  <si>
+    <t>TimeSlice</t>
+  </si>
+  <si>
+    <t>LimType</t>
   </si>
 </sst>
 </file>
@@ -811,68 +808,68 @@
   <sheetData>
     <row r="1" spans="1:1" ht="15">
       <c r="A1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="2" spans="2:9" ht="15">
       <c r="B2" s="1" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
     </row>
     <row r="3" spans="2:9" ht="15.75" thickBot="1">
       <c r="B3" s="3" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="G3" s="4" t="s">
         <v>0</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="4:11" ht="15">
-      <c r="D4" t="s">
-        <v>13</v>
-      </c>
-      <c r="E4">
+      <c r="D4" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="E4" s="7">
         <v>2015</v>
       </c>
-      <c r="F4">
+      <c r="F4" s="7">
         <v>10</v>
       </c>
-      <c r="G4">
+      <c r="G4" s="7">
         <v>10</v>
       </c>
-      <c r="H4" t="s">
-        <v>6</v>
-      </c>
-      <c r="I4" t="s">
-        <v>5</v>
-      </c>
-      <c r="K4" t="s">
-        <v>7</v>
+      <c r="H4" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="K4" s="8" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="4:11" ht="15">
       <c r="D5" s="6" t="s">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="E5" s="7">
         <v>2050</v>
@@ -884,18 +881,18 @@
         <v>20</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K5" s="8" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="4:9" ht="15">
       <c r="D6" t="s">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -907,10 +904,10 @@
         <v>5</v>
       </c>
       <c r="H6" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I6" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/SuppXLS/Scen_NSV_TRADSL_TAX.xlsx
+++ b/SuppXLS/Scen_NSV_TRADSL_TAX.xlsx
@@ -51,49 +51,52 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="15">
+  <si>
+    <t>REG1</t>
+  </si>
+  <si>
+    <t>TimeSlice</t>
+  </si>
+  <si>
+    <t>Trans - Insert</t>
+  </si>
   <si>
     <t>REG2</t>
   </si>
   <si>
-    <t>FLO_TAX</t>
-  </si>
-  <si>
-    <t>TRADSL</t>
-  </si>
-  <si>
-    <t>REG1</t>
-  </si>
-  <si>
-    <t>Year</t>
-  </si>
-  <si>
-    <t>Trans - Insert</t>
-  </si>
-  <si>
-    <t>~TFM_INS</t>
-  </si>
-  <si>
-    <t>Attribute</t>
-  </si>
-  <si>
-    <t>Cset_CN</t>
-  </si>
-  <si>
     <t>Pset_PN</t>
-  </si>
-  <si>
-    <t>TC*</t>
   </si>
   <si>
     <t xml:space="preserve">
 </t>
   </si>
   <si>
-    <t>TimeSlice</t>
+    <t>TRADSL</t>
+  </si>
+  <si>
+    <t>Cset_CN</t>
+  </si>
+  <si>
+    <t>Attribute</t>
+  </si>
+  <si>
+    <t>Year</t>
+  </si>
+  <si>
+    <t>~TFM_INS</t>
   </si>
   <si>
     <t>LimType</t>
+  </si>
+  <si>
+    <t>TC*</t>
+  </si>
+  <si>
+    <t>FLO_TAX</t>
+  </si>
+  <si>
+    <t>gfjh</t>
   </si>
 </sst>
 </file>
@@ -795,7 +798,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:L6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="10.1428571428571" bestFit="1" customWidth="1"/>
@@ -808,45 +811,45 @@
   <sheetData>
     <row r="1" spans="1:1" ht="15">
       <c r="A1" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2" spans="2:9" ht="15">
       <c r="B2" s="1" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
     </row>
     <row r="3" spans="2:9" ht="15.75" thickBot="1">
       <c r="B3" s="3" t="s">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="C3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="4:12" ht="15">
+      <c r="D4" s="6" t="s">
         <v>13</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="H3" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="I3" s="5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="4:11" ht="15">
-      <c r="D4" s="6" t="s">
-        <v>1</v>
       </c>
       <c r="E4" s="7">
         <v>2015</v>
@@ -858,18 +861,21 @@
         <v>10</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K4" s="8" t="s">
-        <v>11</v>
+        <v>5</v>
+      </c>
+      <c r="L4" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="4:11" ht="15">
       <c r="D5" s="6" t="s">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="E5" s="7">
         <v>2050</v>
@@ -881,18 +887,18 @@
         <v>20</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K5" s="8" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="4:9" ht="15">
       <c r="D6" t="s">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -904,10 +910,10 @@
         <v>5</v>
       </c>
       <c r="H6" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I6" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/SuppXLS/Scen_NSV_TRADSL_TAX.xlsx
+++ b/SuppXLS/Scen_NSV_TRADSL_TAX.xlsx
@@ -51,52 +51,49 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="14">
+  <si>
+    <t>Pset_PN</t>
+  </si>
+  <si>
+    <t>TRADSL</t>
+  </si>
+  <si>
+    <t>REG2</t>
+  </si>
   <si>
     <t>REG1</t>
   </si>
   <si>
-    <t>TimeSlice</t>
+    <t>LimType</t>
   </si>
   <si>
     <t>Trans - Insert</t>
   </si>
   <si>
-    <t>REG2</t>
-  </si>
-  <si>
-    <t>Pset_PN</t>
+    <t>Year</t>
+  </si>
+  <si>
+    <t>FLO_TAX</t>
+  </si>
+  <si>
+    <t>Cset_CN</t>
   </si>
   <si>
     <t xml:space="preserve">
 </t>
   </si>
   <si>
-    <t>TRADSL</t>
-  </si>
-  <si>
-    <t>Cset_CN</t>
+    <t>TC*</t>
+  </si>
+  <si>
+    <t>~TFM_INS</t>
+  </si>
+  <si>
+    <t>TimeSlice</t>
   </si>
   <si>
     <t>Attribute</t>
-  </si>
-  <si>
-    <t>Year</t>
-  </si>
-  <si>
-    <t>~TFM_INS</t>
-  </si>
-  <si>
-    <t>LimType</t>
-  </si>
-  <si>
-    <t>TC*</t>
-  </si>
-  <si>
-    <t>FLO_TAX</t>
-  </si>
-  <si>
-    <t>gfjh</t>
   </si>
 </sst>
 </file>
@@ -226,7 +223,7 @@
       <protection/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -244,6 +241,10 @@
       <protection/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" wrapText="1"/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" wrapText="1"/>
       <protection/>
     </xf>
@@ -798,7 +799,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="10.1428571428571" bestFit="1" customWidth="1"/>
@@ -811,45 +812,45 @@
   <sheetData>
     <row r="1" spans="1:1" ht="15">
       <c r="A1" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="2" spans="2:9" ht="15">
       <c r="B2" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
     </row>
     <row r="3" spans="2:9" ht="15.75" thickBot="1">
       <c r="B3" s="3" t="s">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="I3" s="5" t="s">
         <v>8</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="H3" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="I3" s="5" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="4" spans="4:12" ht="15">
       <c r="D4" s="6" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E4" s="7">
         <v>2015</v>
@@ -861,21 +862,21 @@
         <v>10</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K4" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="L4" t="s">
-        <v>14</v>
+        <v>9</v>
+      </c>
+      <c r="L4" s="8" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="4:11" ht="15">
       <c r="D5" s="6" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E5" s="7">
         <v>2050</v>
@@ -887,33 +888,36 @@
         <v>20</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K5" s="8" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="4:13" ht="15">
+      <c r="D6" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E6" s="7">
+        <v>0</v>
+      </c>
+      <c r="F6" s="7">
         <v>5</v>
       </c>
-    </row>
-    <row r="6" spans="4:9" ht="15">
-      <c r="D6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-      <c r="F6">
+      <c r="G6" s="7">
         <v>5</v>
       </c>
-      <c r="G6">
-        <v>5</v>
-      </c>
-      <c r="H6" t="s">
-        <v>12</v>
-      </c>
-      <c r="I6" t="s">
-        <v>6</v>
+      <c r="H6" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="I6" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="M6" s="9" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/SuppXLS/Scen_NSV_TRADSL_TAX.xlsx
+++ b/SuppXLS/Scen_NSV_TRADSL_TAX.xlsx
@@ -51,27 +51,42 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="15">
+  <si>
+    <t>Year</t>
+  </si>
+  <si>
+    <t>~TFM_INS</t>
+  </si>
+  <si>
+    <t>REG1</t>
+  </si>
+  <si>
+    <t>REG2</t>
+  </si>
+  <si>
+    <t>bn,m</t>
+  </si>
+  <si>
+    <t>TRADSL</t>
+  </si>
   <si>
     <t>Pset_PN</t>
   </si>
   <si>
-    <t>TRADSL</t>
-  </si>
-  <si>
-    <t>REG2</t>
-  </si>
-  <si>
-    <t>REG1</t>
-  </si>
-  <si>
     <t>LimType</t>
   </si>
   <si>
+    <t>Attribute</t>
+  </si>
+  <si>
     <t>Trans - Insert</t>
   </si>
   <si>
-    <t>Year</t>
+    <t>TimeSlice</t>
+  </si>
+  <si>
+    <t>TC*</t>
   </si>
   <si>
     <t>FLO_TAX</t>
@@ -82,18 +97,6 @@
   <si>
     <t xml:space="preserve">
 </t>
-  </si>
-  <si>
-    <t>TC*</t>
-  </si>
-  <si>
-    <t>~TFM_INS</t>
-  </si>
-  <si>
-    <t>TimeSlice</t>
-  </si>
-  <si>
-    <t>Attribute</t>
   </si>
 </sst>
 </file>
@@ -812,45 +815,48 @@
   <sheetData>
     <row r="1" spans="1:1" ht="15">
       <c r="A1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="2" spans="2:9" ht="15">
       <c r="B2" s="1" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
     </row>
-    <row r="3" spans="2:9" ht="15.75" thickBot="1">
+    <row r="3" spans="2:13" ht="15.75" thickBot="1">
       <c r="B3" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="M3" t="s">
         <v>4</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="H3" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="I3" s="5" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="4" spans="4:12" ht="15">
       <c r="D4" s="6" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E4" s="7">
         <v>2015</v>
@@ -862,21 +868,21 @@
         <v>10</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K4" s="8" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="L4" s="8" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="4:11" ht="15">
       <c r="D5" s="6" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E5" s="7">
         <v>2050</v>
@@ -888,18 +894,18 @@
         <v>20</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K5" s="8" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="4:13" ht="15">
       <c r="D6" s="6" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E6" s="7">
         <v>0</v>
@@ -911,13 +917,13 @@
         <v>5</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M6" s="9" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/SuppXLS/Scen_NSV_TRADSL_TAX.xlsx
+++ b/SuppXLS/Scen_NSV_TRADSL_TAX.xlsx
@@ -51,9 +51,21 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="15">
-  <si>
-    <t>Year</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="14">
+  <si>
+    <t>Cset_CN</t>
+  </si>
+  <si>
+    <t>TRADSL</t>
+  </si>
+  <si>
+    <t>Pset_PN</t>
+  </si>
+  <si>
+    <t>REG2</t>
+  </si>
+  <si>
+    <t>Attribute</t>
   </si>
   <si>
     <t>~TFM_INS</t>
@@ -62,48 +74,33 @@
     <t>REG1</t>
   </si>
   <si>
-    <t>REG2</t>
-  </si>
-  <si>
-    <t>bn,m</t>
-  </si>
-  <si>
-    <t>TRADSL</t>
-  </si>
-  <si>
-    <t>Pset_PN</t>
-  </si>
-  <si>
-    <t>LimType</t>
-  </si>
-  <si>
-    <t>Attribute</t>
-  </si>
-  <si>
-    <t>Trans - Insert</t>
-  </si>
-  <si>
-    <t>TimeSlice</t>
-  </si>
-  <si>
-    <t>TC*</t>
-  </si>
-  <si>
     <t>FLO_TAX</t>
-  </si>
-  <si>
-    <t>Cset_CN</t>
   </si>
   <si>
     <t xml:space="preserve">
 </t>
+  </si>
+  <si>
+    <t>TC*</t>
+  </si>
+  <si>
+    <t>TimeSlice</t>
+  </si>
+  <si>
+    <t>LimType</t>
+  </si>
+  <si>
+    <t>Year</t>
+  </si>
+  <si>
+    <t>Trans - Insert</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="8">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -153,8 +150,21 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -170,6 +180,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor indexed="44"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF99CCFF"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -226,7 +248,7 @@
       <protection/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -249,6 +271,18 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" wrapText="1"/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment/>
       <protection/>
     </xf>
   </cellXfs>
@@ -815,48 +849,48 @@
   <sheetData>
     <row r="1" spans="1:1" ht="15">
       <c r="A1" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2" spans="2:9" ht="15">
       <c r="B2" s="1" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
     </row>
     <row r="3" spans="2:13" ht="15.75" thickBot="1">
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" s="3" t="s">
+      <c r="C3" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="G3" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="H3" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="I3" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="M3" s="8" t="s">
         <v>8</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="H3" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="I3" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="M3" t="s">
-        <v>4</v>
       </c>
     </row>
     <row r="4" spans="4:12" ht="15">
       <c r="D4" s="6" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E4" s="7">
         <v>2015</v>
@@ -868,21 +902,21 @@
         <v>10</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K4" s="8" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="L4" s="8" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="4:11" ht="15">
       <c r="D5" s="6" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E5" s="7">
         <v>2050</v>
@@ -894,18 +928,18 @@
         <v>20</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K5" s="8" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="4:13" ht="15">
       <c r="D6" s="6" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E6" s="7">
         <v>0</v>
@@ -917,13 +951,13 @@
         <v>5</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M6" s="9" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/SuppXLS/Scen_NSV_TRADSL_TAX.xlsx
+++ b/SuppXLS/Scen_NSV_TRADSL_TAX.xlsx
@@ -51,27 +51,36 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="15">
+  <si>
+    <t>Attribute</t>
+  </si>
+  <si>
+    <t>~TFM_INS</t>
+  </si>
+  <si>
+    <t>Year</t>
+  </si>
+  <si>
+    <t>REG1</t>
+  </si>
   <si>
     <t>Cset_CN</t>
   </si>
   <si>
-    <t>TRADSL</t>
-  </si>
-  <si>
-    <t>Pset_PN</t>
+    <t>TC*</t>
   </si>
   <si>
     <t>REG2</t>
   </si>
   <si>
-    <t>Attribute</t>
-  </si>
-  <si>
-    <t>~TFM_INS</t>
-  </si>
-  <si>
-    <t>REG1</t>
+    <t>LimType</t>
+  </si>
+  <si>
+    <t>Trans - Insert</t>
+  </si>
+  <si>
+    <t>TimeSlice</t>
   </si>
   <si>
     <t>FLO_TAX</t>
@@ -81,19 +90,13 @@
 </t>
   </si>
   <si>
-    <t>TC*</t>
-  </si>
-  <si>
-    <t>TimeSlice</t>
-  </si>
-  <si>
-    <t>LimType</t>
-  </si>
-  <si>
-    <t>Year</t>
-  </si>
-  <si>
-    <t>Trans - Insert</t>
+    <t>Pset_PN</t>
+  </si>
+  <si>
+    <t>TRADSL</t>
+  </si>
+  <si>
+    <t>yjhbj</t>
   </si>
 </sst>
 </file>
@@ -849,48 +852,48 @@
   <sheetData>
     <row r="1" spans="1:1" ht="15">
       <c r="A1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="2" spans="2:9" ht="15">
       <c r="B2" s="1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
     </row>
     <row r="3" spans="2:13" ht="15.75" thickBot="1">
       <c r="B3" s="10" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C3" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="F3" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="G3" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="H3" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="I3" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="M3" s="8" t="s">
         <v>11</v>
-      </c>
-      <c r="D3" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="E3" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="F3" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="G3" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="H3" s="12" t="s">
-        <v>2</v>
-      </c>
-      <c r="I3" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="M3" s="8" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="4" spans="4:12" ht="15">
       <c r="D4" s="6" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E4" s="7">
         <v>2015</v>
@@ -902,21 +905,21 @@
         <v>10</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="K4" s="8" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="L4" s="8" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="4:11" ht="15">
       <c r="D5" s="6" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E5" s="7">
         <v>2050</v>
@@ -928,18 +931,18 @@
         <v>20</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="K5" s="8" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="4:13" ht="15">
       <c r="D6" s="6" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E6" s="7">
         <v>0</v>
@@ -951,13 +954,13 @@
         <v>5</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="M6" s="9" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/SuppXLS/Scen_NSV_TRADSL_TAX.xlsx
+++ b/SuppXLS/Scen_NSV_TRADSL_TAX.xlsx
@@ -51,52 +51,49 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="15">
-  <si>
-    <t>Attribute</t>
-  </si>
-  <si>
-    <t>~TFM_INS</t>
-  </si>
-  <si>
-    <t>Year</t>
-  </si>
-  <si>
-    <t>REG1</t>
-  </si>
-  <si>
-    <t>Cset_CN</t>
-  </si>
-  <si>
-    <t>TC*</t>
-  </si>
-  <si>
-    <t>REG2</t>
-  </si>
-  <si>
-    <t>LimType</t>
-  </si>
-  <si>
-    <t>Trans - Insert</t>
-  </si>
-  <si>
-    <t>TimeSlice</t>
-  </si>
-  <si>
-    <t>FLO_TAX</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="14">
   <si>
     <t xml:space="preserve">
 </t>
   </si>
   <si>
+    <t>TRADSL</t>
+  </si>
+  <si>
+    <t>Cset_CN</t>
+  </si>
+  <si>
     <t>Pset_PN</t>
   </si>
   <si>
-    <t>TRADSL</t>
-  </si>
-  <si>
-    <t>yjhbj</t>
+    <t>Year</t>
+  </si>
+  <si>
+    <t>TimeSlice</t>
+  </si>
+  <si>
+    <t>REG2</t>
+  </si>
+  <si>
+    <t>FLO_TAX</t>
+  </si>
+  <si>
+    <t>TC*</t>
+  </si>
+  <si>
+    <t>LimType</t>
+  </si>
+  <si>
+    <t>Attribute</t>
+  </si>
+  <si>
+    <t>REG1</t>
+  </si>
+  <si>
+    <t>~TFM_INS</t>
+  </si>
+  <si>
+    <t>Trans - Insert</t>
   </si>
 </sst>
 </file>
@@ -251,7 +248,7 @@
       <protection/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -286,6 +283,10 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" wrapText="1"/>
       <protection/>
     </xf>
   </cellXfs>
@@ -852,48 +853,48 @@
   <sheetData>
     <row r="1" spans="1:1" ht="15">
       <c r="A1" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2" spans="2:9" ht="15">
       <c r="B2" s="1" t="s">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
     </row>
     <row r="3" spans="2:13" ht="15.75" thickBot="1">
       <c r="B3" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="10" t="s">
-        <v>7</v>
-      </c>
       <c r="D3" s="10" t="s">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F3" s="11" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="G3" s="11" t="s">
         <v>6</v>
       </c>
       <c r="H3" s="12" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="I3" s="12" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M3" s="8" t="s">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="4:12" ht="15">
       <c r="D4" s="6" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E4" s="7">
         <v>2015</v>
@@ -905,21 +906,21 @@
         <v>10</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="K4" s="8" t="s">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="L4" s="8" t="s">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="4:11" ht="15">
       <c r="D5" s="6" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E5" s="7">
         <v>2050</v>
@@ -931,18 +932,18 @@
         <v>20</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="K5" s="8" t="s">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="4:13" ht="15">
       <c r="D6" s="6" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E6" s="7">
         <v>0</v>
@@ -954,13 +955,13 @@
         <v>5</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="M6" s="9" t="s">
-        <v>14</v>
+        <v>1</v>
+      </c>
+      <c r="M6" s="13" t="s">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/SuppXLS/Scen_NSV_TRADSL_TAX.xlsx
+++ b/SuppXLS/Scen_NSV_TRADSL_TAX.xlsx
@@ -51,49 +51,52 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="15">
+  <si>
+    <t>Trans - Insert</t>
+  </si>
+  <si>
+    <t>~TFM_INS</t>
+  </si>
+  <si>
+    <t>Attribute</t>
+  </si>
+  <si>
+    <t>Year</t>
+  </si>
+  <si>
+    <t>Pset_PN</t>
+  </si>
+  <si>
+    <t>FLO_TAX</t>
+  </si>
+  <si>
+    <t>REG1</t>
+  </si>
+  <si>
+    <t>LimType</t>
+  </si>
+  <si>
+    <t>TimeSlice</t>
+  </si>
   <si>
     <t xml:space="preserve">
 </t>
   </si>
   <si>
+    <t>Cset_CN</t>
+  </si>
+  <si>
+    <t>REG2</t>
+  </si>
+  <si>
+    <t>TC*</t>
+  </si>
+  <si>
     <t>TRADSL</t>
   </si>
   <si>
-    <t>Cset_CN</t>
-  </si>
-  <si>
-    <t>Pset_PN</t>
-  </si>
-  <si>
-    <t>Year</t>
-  </si>
-  <si>
-    <t>TimeSlice</t>
-  </si>
-  <si>
-    <t>REG2</t>
-  </si>
-  <si>
-    <t>FLO_TAX</t>
-  </si>
-  <si>
-    <t>TC*</t>
-  </si>
-  <si>
-    <t>LimType</t>
-  </si>
-  <si>
-    <t>Attribute</t>
-  </si>
-  <si>
-    <t>REG1</t>
-  </si>
-  <si>
-    <t>~TFM_INS</t>
-  </si>
-  <si>
-    <t>Trans - Insert</t>
+    <t>adeads</t>
   </si>
 </sst>
 </file>
@@ -853,48 +856,48 @@
   <sheetData>
     <row r="1" spans="1:1" ht="15">
       <c r="A1" t="s">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2" spans="2:9" ht="15">
       <c r="B2" s="1" t="s">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
     </row>
     <row r="3" spans="2:13" ht="15.75" thickBot="1">
       <c r="B3" s="10" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C3" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="F3" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="G3" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="H3" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="I3" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="M3" s="8" t="s">
         <v>9</v>
-      </c>
-      <c r="D3" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="F3" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="G3" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="H3" s="12" t="s">
-        <v>3</v>
-      </c>
-      <c r="I3" s="12" t="s">
-        <v>2</v>
-      </c>
-      <c r="M3" s="8" t="s">
-        <v>0</v>
       </c>
     </row>
     <row r="4" spans="4:12" ht="15">
       <c r="D4" s="6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E4" s="7">
         <v>2015</v>
@@ -906,21 +909,21 @@
         <v>10</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="K4" s="8" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L4" s="8" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
-    <row r="5" spans="4:11" ht="15">
+    <row r="5" spans="4:12" ht="15">
       <c r="D5" s="6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E5" s="7">
         <v>2050</v>
@@ -932,18 +935,21 @@
         <v>20</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="K5" s="8" t="s">
-        <v>0</v>
+        <v>9</v>
+      </c>
+      <c r="L5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="4:13" ht="15">
       <c r="D6" s="6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E6" s="7">
         <v>0</v>
@@ -955,13 +961,13 @@
         <v>5</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="M6" s="13" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/SuppXLS/Scen_NSV_TRADSL_TAX.xlsx
+++ b/SuppXLS/Scen_NSV_TRADSL_TAX.xlsx
@@ -51,33 +51,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="15">
-  <si>
-    <t>Trans - Insert</t>
-  </si>
-  <si>
-    <t>~TFM_INS</t>
-  </si>
-  <si>
-    <t>Attribute</t>
-  </si>
-  <si>
-    <t>Year</t>
-  </si>
-  <si>
-    <t>Pset_PN</t>
-  </si>
-  <si>
-    <t>FLO_TAX</t>
-  </si>
-  <si>
-    <t>REG1</t>
-  </si>
-  <si>
-    <t>LimType</t>
-  </si>
-  <si>
-    <t>TimeSlice</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="14">
+  <si>
+    <t>TRADSL</t>
   </si>
   <si>
     <t xml:space="preserve">
@@ -87,16 +63,37 @@
     <t>Cset_CN</t>
   </si>
   <si>
+    <t>REG1</t>
+  </si>
+  <si>
+    <t>LimType</t>
+  </si>
+  <si>
+    <t>Pset_PN</t>
+  </si>
+  <si>
+    <t>FLO_TAX</t>
+  </si>
+  <si>
+    <t>TC*</t>
+  </si>
+  <si>
+    <t>Trans - Insert</t>
+  </si>
+  <si>
+    <t>Year</t>
+  </si>
+  <si>
     <t>REG2</t>
   </si>
   <si>
-    <t>TC*</t>
-  </si>
-  <si>
-    <t>TRADSL</t>
-  </si>
-  <si>
-    <t>adeads</t>
+    <t>TimeSlice</t>
+  </si>
+  <si>
+    <t>~TFM_INS</t>
+  </si>
+  <si>
+    <t>Attribute</t>
   </si>
 </sst>
 </file>
@@ -856,48 +853,48 @@
   <sheetData>
     <row r="1" spans="1:1" ht="15">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="2" spans="2:9" ht="15">
       <c r="B2" s="1" t="s">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
     </row>
     <row r="3" spans="2:13" ht="15.75" thickBot="1">
       <c r="B3" s="10" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D3" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="G3" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="H3" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="I3" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="F3" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="G3" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="H3" s="12" t="s">
-        <v>4</v>
-      </c>
-      <c r="I3" s="12" t="s">
-        <v>10</v>
-      </c>
       <c r="M3" s="8" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="4:12" ht="15">
       <c r="D4" s="6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E4" s="7">
         <v>2015</v>
@@ -909,21 +906,21 @@
         <v>10</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="K4" s="8" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="L4" s="8" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="4:12" ht="15">
       <c r="D5" s="6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E5" s="7">
         <v>2050</v>
@@ -935,21 +932,21 @@
         <v>20</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="K5" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="L5" t="s">
-        <v>14</v>
+        <v>1</v>
+      </c>
+      <c r="L5" s="8" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="4:13" ht="15">
       <c r="D6" s="6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E6" s="7">
         <v>0</v>
@@ -961,13 +958,13 @@
         <v>5</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="M6" s="13" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/SuppXLS/Scen_NSV_TRADSL_TAX.xlsx
+++ b/SuppXLS/Scen_NSV_TRADSL_TAX.xlsx
@@ -51,49 +51,52 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="15">
+  <si>
+    <t>~TFM_INS</t>
+  </si>
+  <si>
+    <t>Trans - Insert</t>
+  </si>
+  <si>
+    <t>Attribute</t>
+  </si>
+  <si>
+    <t>REG2</t>
+  </si>
+  <si>
+    <t>hjkj</t>
+  </si>
+  <si>
+    <t>Year</t>
+  </si>
+  <si>
+    <t>LimType</t>
+  </si>
+  <si>
+    <t>TimeSlice</t>
+  </si>
   <si>
     <t>TRADSL</t>
+  </si>
+  <si>
+    <t>Pset_PN</t>
+  </si>
+  <si>
+    <t>REG1</t>
+  </si>
+  <si>
+    <t>FLO_TAX</t>
+  </si>
+  <si>
+    <t>TC*</t>
+  </si>
+  <si>
+    <t>Cset_CN</t>
   </si>
   <si>
     <t xml:space="preserve">
 </t>
-  </si>
-  <si>
-    <t>Cset_CN</t>
-  </si>
-  <si>
-    <t>REG1</t>
-  </si>
-  <si>
-    <t>LimType</t>
-  </si>
-  <si>
-    <t>Pset_PN</t>
-  </si>
-  <si>
-    <t>FLO_TAX</t>
-  </si>
-  <si>
-    <t>TC*</t>
-  </si>
-  <si>
-    <t>Trans - Insert</t>
-  </si>
-  <si>
-    <t>Year</t>
-  </si>
-  <si>
-    <t>REG2</t>
-  </si>
-  <si>
-    <t>TimeSlice</t>
-  </si>
-  <si>
-    <t>~TFM_INS</t>
-  </si>
-  <si>
-    <t>Attribute</t>
   </si>
 </sst>
 </file>
@@ -853,48 +856,48 @@
   <sheetData>
     <row r="1" spans="1:1" ht="15">
       <c r="A1" t="s">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2" spans="2:9" ht="15">
       <c r="B2" s="1" t="s">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
     </row>
     <row r="3" spans="2:13" ht="15.75" thickBot="1">
       <c r="B3" s="10" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C3" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="F3" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="G3" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="H3" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="I3" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="M3" s="8" t="s">
         <v>4</v>
-      </c>
-      <c r="D3" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="E3" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="G3" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="H3" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="I3" s="12" t="s">
-        <v>2</v>
-      </c>
-      <c r="M3" s="8" t="s">
-        <v>1</v>
       </c>
     </row>
     <row r="4" spans="4:12" ht="15">
       <c r="D4" s="6" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E4" s="7">
         <v>2015</v>
@@ -906,21 +909,21 @@
         <v>10</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K4" s="8" t="s">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="L4" s="8" t="s">
-        <v>1</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="4:12" ht="15">
       <c r="D5" s="6" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E5" s="7">
         <v>2050</v>
@@ -932,21 +935,21 @@
         <v>20</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K5" s="8" t="s">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="L5" s="8" t="s">
-        <v>1</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="4:13" ht="15">
       <c r="D6" s="6" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E6" s="7">
         <v>0</v>
@@ -958,13 +961,13 @@
         <v>5</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M6" s="13" t="s">
-        <v>1</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
